--- a/KatalonData/RADTestData/FEINmismatch.xlsx
+++ b/KatalonData/RADTestData/FEINmismatch.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="136">
   <si>
     <t>Result</t>
   </si>
@@ -292,12 +292,166 @@
   </si>
   <si>
     <t>Sun Aug 02 19:24:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:49:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:49:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:50:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:50:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:51:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:51:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:52:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:52:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:53:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:53:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:54:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:54:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:55:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:55:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:56:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:56:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:57:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:57:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:57:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:58:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:58:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:59:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 01:59:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:00:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:00:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:01:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:01:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:02:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:02:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:03:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:17:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:17:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:18:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:19:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:19:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:20:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:21:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:22:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:23:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:23:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:25:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:26:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:28:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:30:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:30:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:31:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:32:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:33:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:33:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:34:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:34:58 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -664,12 +818,12 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="48" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="43.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="48.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="43.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -694,7 +848,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -711,7 +865,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -728,7 +882,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -745,7 +899,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -762,7 +916,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -779,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -796,7 +950,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -813,7 +967,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -830,7 +984,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -847,7 +1001,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -864,7 +1018,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -881,7 +1035,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -898,7 +1052,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -915,7 +1069,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -932,7 +1086,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -949,7 +1103,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -966,7 +1120,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -983,7 +1137,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1000,7 +1154,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1017,7 +1171,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -1034,7 +1188,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1051,7 +1205,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -1068,7 +1222,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -1085,7 +1239,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
@@ -1102,7 +1256,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>5</v>
@@ -1119,7 +1273,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>5</v>
@@ -1136,7 +1290,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -1153,7 +1307,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -1170,7 +1324,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -1187,7 +1341,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
@@ -1212,12 +1366,12 @@
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="47.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="43.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="47.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="43.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -1242,7 +1396,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -1259,7 +1413,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -1276,7 +1430,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -1293,7 +1447,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -1310,7 +1464,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -1327,7 +1481,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -1344,7 +1498,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -1361,7 +1515,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -1378,7 +1532,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -1395,7 +1549,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1412,7 +1566,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -1429,7 +1583,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -1446,7 +1600,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -1463,7 +1617,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -1480,7 +1634,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -1497,7 +1651,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -1514,7 +1668,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -1531,7 +1685,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1548,7 +1702,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1576,7 +1730,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1614,8 +1768,8 @@
       <c r="A25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B25" t="s">
-        <v>84</v>
+      <c r="B25" t="s" s="1">
+        <v>135</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>

--- a/KatalonData/RADTestData/FEINmismatch.xlsx
+++ b/KatalonData/RADTestData/FEINmismatch.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="136">
   <si>
     <t>Result</t>
   </si>
@@ -292,12 +292,166 @@
   </si>
   <si>
     <t>Sun Aug 02 19:24:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:00:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:00:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:00:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:00:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:00:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:01:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:01:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:01:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:01:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:01:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:02:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:02:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:02:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:02:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:02:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:02:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:03:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:03:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:03:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:03:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:03:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:03:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:04:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:04:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:04:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:04:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:04:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:04:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:05:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:05:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:10:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:10:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:10:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:10:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:11:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:11:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:11:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:11:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:11:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:11:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:12:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:12:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:12:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:12:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:12:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:12:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:13:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:13:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:13:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:13:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:13:43 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -664,12 +818,12 @@
   <dimension ref="A1:E31"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="48" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="43.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="48.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="43.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -694,7 +848,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -711,7 +865,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>86</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -728,7 +882,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -745,7 +899,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -762,7 +916,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -779,7 +933,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -796,7 +950,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>91</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -813,7 +967,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -830,7 +984,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -847,7 +1001,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -864,7 +1018,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -881,7 +1035,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -898,7 +1052,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -915,7 +1069,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>47</v>
+        <v>98</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -932,7 +1086,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -949,7 +1103,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>49</v>
+        <v>100</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -966,7 +1120,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -983,7 +1137,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>51</v>
+        <v>102</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1000,7 +1154,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>52</v>
+        <v>103</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1017,7 +1171,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>53</v>
+        <v>104</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>5</v>
@@ -1034,7 +1188,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1051,7 +1205,7 @@
         <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>55</v>
+        <v>106</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>5</v>
@@ -1068,7 +1222,7 @@
         <v>14</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
@@ -1085,7 +1239,7 @@
         <v>14</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
@@ -1102,7 +1256,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>5</v>
@@ -1119,7 +1273,7 @@
         <v>14</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>59</v>
+        <v>110</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>5</v>
@@ -1136,7 +1290,7 @@
         <v>14</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>5</v>
@@ -1153,7 +1307,7 @@
         <v>14</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>5</v>
@@ -1170,7 +1324,7 @@
         <v>14</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>5</v>
@@ -1187,7 +1341,7 @@
         <v>14</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>5</v>
@@ -1212,12 +1366,12 @@
   <dimension ref="A1:E25"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="47.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="43.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="47.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="43.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.45">
@@ -1242,7 +1396,7 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>64</v>
+        <v>115</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>5</v>
@@ -1259,7 +1413,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>65</v>
+        <v>116</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -1276,7 +1430,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>5</v>
@@ -1293,7 +1447,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>118</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -1310,7 +1464,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>5</v>
@@ -1327,7 +1481,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>5</v>
@@ -1344,7 +1498,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>5</v>
@@ -1361,7 +1515,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>71</v>
+        <v>122</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>5</v>
@@ -1378,7 +1532,7 @@
         <v>14</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>5</v>
@@ -1395,7 +1549,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>73</v>
+        <v>124</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>5</v>
@@ -1412,7 +1566,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>5</v>
@@ -1429,7 +1583,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>5</v>
@@ -1446,7 +1600,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>5</v>
@@ -1463,7 +1617,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -1480,7 +1634,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>5</v>
@@ -1497,7 +1651,7 @@
         <v>14</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>5</v>
@@ -1514,7 +1668,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>5</v>
@@ -1531,7 +1685,7 @@
         <v>14</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>5</v>
@@ -1548,7 +1702,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>82</v>
+        <v>133</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>5</v>
@@ -1576,7 +1730,7 @@
         <v>14</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>5</v>
@@ -1614,8 +1768,8 @@
       <c r="A25" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B25" t="s">
-        <v>84</v>
+      <c r="B25" t="s" s="1">
+        <v>135</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>5</v>
